--- a/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 28,28</t>
+          <t>9,17; 28,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,32; 33,57</t>
+          <t>15,51; 34,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 28,71</t>
+          <t>14,83; 28,98</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,14</t>
+          <t>7,13; 12,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,67</t>
+          <t>7,16; 11,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,11</t>
+          <t>7,74; 11,22</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,4</t>
+          <t>1,68; 7,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,7</t>
+          <t>1,33; 5,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,33</t>
+          <t>1,92; 5,42</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,0</t>
+          <t>6,98; 10,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,96</t>
+          <t>7,24; 10,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,42</t>
+          <t>7,63; 10,34</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14429</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23761</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4785; 14820</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9320; 20815</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16650; 32548</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>43101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46578</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89679</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>32134; 54905</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36044; 60298</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>73837; 107067</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5265</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10954</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2507; 10617</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2399; 10717</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6315; 17866</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>58120</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66273</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124393</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>45492; 71648</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>53846; 81387</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106580; 144431</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 28,39</t>
+          <t>9,79; 28,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 34,64</t>
+          <t>15,3; 35,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,83; 28,98</t>
+          <t>14,74; 28,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,18</t>
+          <t>7,11; 12,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,97</t>
+          <t>7,06; 11,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,22</t>
+          <t>7,81; 11,28</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,12</t>
+          <t>1,84; 7,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,94</t>
+          <t>1,26; 5,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,42</t>
+          <t>1,95; 5,26</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,99</t>
+          <t>6,75; 11,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,94</t>
+          <t>7,25; 11,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,34</t>
+          <t>7,56; 10,33</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4785; 14820</t>
+          <t>5110; 15026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9320; 20815</t>
+          <t>9197; 21200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16650; 32548</t>
+          <t>16552; 32536</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32134; 54905</t>
+          <t>32045; 56255</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36044; 60298</t>
+          <t>35568; 60412</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73837; 107067</t>
+          <t>74571; 107665</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2507; 10617</t>
+          <t>2742; 11199</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2399; 10717</t>
+          <t>2269; 10748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6315; 17866</t>
+          <t>6435; 17343</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45492; 71648</t>
+          <t>43995; 71708</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53846; 81387</t>
+          <t>53950; 82476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106580; 144431</t>
+          <t>105592; 144159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 28,79</t>
+          <t>16,22; 35,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,3; 35,28</t>
+          <t>12,64; 32,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 28,97</t>
+          <t>16,94; 31,34</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 12,48</t>
+          <t>7,37; 12,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,99</t>
+          <t>8,1; 13,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,28</t>
+          <t>8,29; 11,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,51</t>
+          <t>1,53; 6,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,96</t>
+          <t>1,79; 7,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,26</t>
+          <t>2,01; 6,01</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,0</t>
+          <t>7,62; 11,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,08</t>
+          <t>7,88; 12,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,33</t>
+          <t>8,1; 10,99</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>23457</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5110; 15026</t>
+          <t>8893; 19648</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9197; 21200</t>
+          <t>5613; 14539</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16552; 32536</t>
+          <t>16815; 31104</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>43101</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46578</t>
+          <t>43589</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89679</t>
+          <t>88437</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32045; 56255</t>
+          <t>34122; 56645</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35568; 60412</t>
+          <t>34241; 55202</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74571; 107665</t>
+          <t>73402; 104646</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>11781</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2742; 11199</t>
+          <t>2526; 10897</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2269; 10748</t>
+          <t>2685; 11670</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6435; 17343</t>
+          <t>6325; 18941</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>123676</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43995; 71708</t>
+          <t>52080; 79556</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53950; 82476</t>
+          <t>48592; 74042</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105592; 144159</t>
+          <t>105345; 142901</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16,22; 35,84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12,64; 32,73</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16,94; 31,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 12,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8,1; 13,05</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8,29; 11,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 6,59</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,79; 7,8</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,01; 6,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,62; 11,65</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,88; 12,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,1; 10,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2536512076101984</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2150023647680726</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2363527851318173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>13907</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9551</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23457</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1621986558820226</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1263674590800566</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.169422969854934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8893; 19648</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5613; 14539</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16815; 31104</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3583711401052337</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3273103504601975</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3134040096792236</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.09690090176396061</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1030844158516586</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.09985309775617306</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>44848</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>43589</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88437</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.07372532584114909</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.08097624141469853</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.08287732773804619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>34122; 56645</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34241; 55202</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>73402; 104646</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1223894316422499</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.130549189937033</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1181544315271685</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.03394840424799286</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.04119930299907679</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.03739207739172016</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5616</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6165</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11781</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.0152719895913904</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01794049949192608</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.02007543931746557</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2526; 10897</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2685; 11670</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6325; 18941</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.06586996816540343</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.07799016153749382</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.06011618907478943</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.09423580116271311</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.0961323140674791</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.09513578263351097</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>64371</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>59305</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>123676</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.07624276757825967</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.07876727035487753</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.08103488366238508</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>52080; 79556</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>48592; 74042</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>105345; 142901</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1164652119498361</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1200224591607166</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.109924892575159</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>13907</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9551</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>23457</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>8893</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5613</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>16815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>19648</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>14539</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>31104</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>44848</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>43589</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>88437</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>34122</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>34241</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>73402</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>56645</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>55202</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>104646</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>5616</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>6165</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>11781</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>2526</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2685</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>6325</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>10897</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11670</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>18941</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>64371</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>59305</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>123676</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>52080</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>48592</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>105345</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>74042</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>142901</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>